--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487171_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487171_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3709</v>
+        <v>2.8309</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5755</v>
+        <v>0.5537</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7953</v>
+        <v>2.2772</v>
       </c>
       <c r="G2" t="n">
         <v>0.5636</v>
@@ -610,13 +610,13 @@
         <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0383</v>
+        <v>0.4217</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3081</v>
+        <v>0.2862</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3464</v>
+        <v>0.1355</v>
       </c>
       <c r="V2" t="n">
         <v>-0.08450000000000001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0286</v>
+        <v>1.273</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0483</v>
+        <v>0.2661</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9802</v>
+        <v>1.007</v>
       </c>
       <c r="G3" t="n">
         <v>1.7884</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1296</v>
+        <v>0.3741</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9915</v>
+        <v>0.2092</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1381</v>
+        <v>0.1649</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6965</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4771</v>
+        <v>1.0363</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.1951</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0018</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5204</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.271</v>
+        <v>0.2882</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.612</v>
+        <v>0.1078</v>
       </c>
       <c r="U4" t="n">
-        <v>0.341</v>
+        <v>0.1804</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0825</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1522</v>
+        <v>0.3718</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4302</v>
+        <v>-0.5049</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2779</v>
+        <v>0.8767</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1806</v>
+        <v>0.1007</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1335</v>
+        <v>-0.3405</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0471</v>
+        <v>0.4413</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5941</v>
+        <v>-0.6269</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.6676</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5941</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4134</v>
+        <v>0.7277</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1335</v>
+        <v>0.3271</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5469000000000001</v>
+        <v>0.4006</v>
       </c>
       <c r="P5" t="n">
-        <v>0.579</v>
+        <v>0.193</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>0.193</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0357</v>
+        <v>0.078</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1639</v>
+        <v>0.122</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1282</v>
+        <v>-0.044</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0625</v>
+        <v>0.0987</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8054</v>
+        <v>0.4302</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7429</v>
+        <v>-0.3314</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1007</v>
+        <v>0.1806</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3405</v>
+        <v>0.1335</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4413</v>
+        <v>0.0471</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6269</v>
+        <v>0.5941</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6676</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>0.5941</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7277</v>
+        <v>-0.4134</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3271</v>
+        <v>0.1335</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4006</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3563</v>
+        <v>-0.0892</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1785</v>
+        <v>-0.1639</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1778</v>
+        <v>0.0747</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8758</v>
+        <v>-0.9502</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.792</v>
+        <v>-1.7325</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9161</v>
+        <v>0.7823</v>
       </c>
       <c r="G7" t="n">
         <v>-2.7111</v>
@@ -1000,13 +1000,13 @@
         <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9631</v>
+        <v>0.8887</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3966</v>
+        <v>0.4561</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5664</v>
+        <v>0.4326</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2859</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7109</v>
+        <v>-4.0568</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7581</v>
+        <v>-4.2771</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.469</v>
+        <v>0.2203</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8023</v>
+        <v>-5.4206</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2854</v>
+        <v>-0.4988</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5169</v>
+        <v>-4.9217</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1667</v>
+        <v>-3.6263</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5641</v>
+        <v>0.1758</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6026</v>
+        <v>-3.8021</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6356</v>
+        <v>-1.7943</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.6747</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9143</v>
+        <v>-1.1196</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7371</v>
+        <v>2.8951</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1787</v>
+        <v>0.7671</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9249</v>
+        <v>0.0513</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2538</v>
+        <v>0.7158</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.8243</v>
+        <v>-0.3684</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.8243</v>
+        <v>-1.5964</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1623</v>
+        <v>-4.1129</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.7574</v>
+        <v>-0.6438</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5951</v>
+        <v>-3.469</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.4206</v>
+        <v>-3.8023</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4988</v>
+        <v>-1.2854</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.9217</v>
+        <v>-2.5169</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.6263</v>
+        <v>-1.1667</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1758</v>
+        <v>-0.5641</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.8021</v>
+        <v>-0.6026</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7943</v>
+        <v>-2.6356</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6747</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1196</v>
+        <v>-1.9143</v>
       </c>
       <c r="P9" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8951</v>
+        <v>1.7371</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3384</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.429</v>
+        <v>0.5229</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0906</v>
+        <v>0.2538</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3684</v>
+        <v>-2.8243</v>
       </c>
       <c r="W9" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5964</v>
+        <v>-2.8243</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4284</v>
+        <v>-4.6272</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0684</v>
+        <v>-4.5082</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.36</v>
+        <v>-0.1191</v>
       </c>
       <c r="G10" t="n">
         <v>-4.2512</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7912</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.155</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.076</v>
+        <v>0.1649</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.1866</v>
+        <v>-7.369</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.343</v>
+        <v>-8.364800000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1564</v>
+        <v>0.9958</v>
       </c>
       <c r="G11" t="n">
         <v>-9.023</v>
@@ -1312,13 +1312,13 @@
         <v>3.2811</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1819</v>
+        <v>0.9994</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4099</v>
+        <v>0.3881</v>
       </c>
       <c r="U11" t="n">
-        <v>0.772</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6965</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.3977</v>
+        <v>-15.5054</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.4788</v>
+        <v>-18.5862</v>
       </c>
       <c r="F12" t="n">
-        <v>3.080900000000001</v>
+        <v>3.081</v>
       </c>
       <c r="G12" t="n">
         <v>-23.0953</v>
@@ -1369,7 +1369,7 @@
         <v>-6.573700000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.450900000000001</v>
+        <v>-6.450899999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-10.0706</v>
@@ -1390,13 +1390,13 @@
         <v>19.3008</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6224</v>
+        <v>4.5146</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9324000000000001</v>
+        <v>1.8247</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6899</v>
+        <v>2.69</v>
       </c>
       <c r="V12" t="n">
         <v>-5.610300000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9678</v>
+        <v>6.8581</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1906</v>
+        <v>1.5911</v>
       </c>
       <c r="F13" t="n">
-        <v>5.7772</v>
+        <v>5.2669</v>
       </c>
       <c r="G13" t="n">
         <v>5.1035</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9597</v>
+        <v>0.85</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9967</v>
+        <v>-0.5962</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9564</v>
+        <v>1.4462</v>
       </c>
       <c r="V13" t="n">
         <v>3.0277</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6405</v>
+        <v>6.417</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1812</v>
+        <v>1.7425</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4593</v>
+        <v>4.6745</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4322</v>
+        <v>6.6406</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5493</v>
+        <v>2.9984</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1171</v>
+        <v>3.6422</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3436</v>
+        <v>3.0683</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8484</v>
+        <v>1.009</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5048</v>
+        <v>2.0592</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0885</v>
+        <v>3.5723</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7008</v>
+        <v>1.9894</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3877</v>
+        <v>1.583</v>
       </c>
       <c r="P14" t="n">
-        <v>0.579</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R14" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9731</v>
+        <v>-0.1355</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8376</v>
+        <v>-0.2726</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1355</v>
+        <v>0.1371</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6562</v>
+        <v>1.842</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1941</v>
+        <v>5.3646</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2418</v>
+        <v>2.9895</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9524</v>
+        <v>2.3751</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6406</v>
+        <v>2.6484</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9984</v>
+        <v>-0.2184</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6422</v>
+        <v>2.8668</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0683</v>
+        <v>1.546</v>
       </c>
       <c r="K15" t="n">
-        <v>1.009</v>
+        <v>-0.2848</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0592</v>
+        <v>1.8308</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5723</v>
+        <v>1.1024</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9894</v>
+        <v>0.0664</v>
       </c>
       <c r="O15" t="n">
-        <v>1.583</v>
+        <v>1.036</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.386</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.9301</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R15" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3583</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7733</v>
+        <v>-0.3103</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.585</v>
+        <v>0.3004</v>
       </c>
       <c r="V15" t="n">
-        <v>1.842</v>
+        <v>3.1122</v>
       </c>
       <c r="W15" t="n">
-        <v>1.842</v>
+        <v>3.6839</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6362</v>
+        <v>4.2403</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0897</v>
+        <v>3.4807</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5466</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6484</v>
+        <v>3.5753</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2184</v>
+        <v>0.6107</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8668</v>
+        <v>2.9646</v>
       </c>
       <c r="J16" t="n">
-        <v>1.546</v>
+        <v>3.8419</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2848</v>
+        <v>0.7245</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8308</v>
+        <v>3.1174</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1024</v>
+        <v>-0.2665</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0664</v>
+        <v>-0.1137</v>
       </c>
       <c r="O16" t="n">
-        <v>1.036</v>
+        <v>-0.1528</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.386</v>
+        <v>0.965</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7383</v>
+        <v>-0.3001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2102</v>
+        <v>-0.3612</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5282</v>
+        <v>0.0611</v>
       </c>
       <c r="V16" t="n">
-        <v>3.1122</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.6839</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8734</v>
+        <v>3.4959</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3805</v>
+        <v>0.6791</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4929</v>
+        <v>2.8168</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5753</v>
+        <v>1.4322</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6107</v>
+        <v>1.5493</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9646</v>
+        <v>-0.1171</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8419</v>
+        <v>0.3436</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7245</v>
+        <v>0.8484</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1174</v>
+        <v>-0.5048</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2665</v>
+        <v>1.0885</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1137</v>
+        <v>0.7008</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1528</v>
+        <v>0.3877</v>
       </c>
       <c r="P17" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6669</v>
+        <v>0.8285</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4614</v>
+        <v>0.3355</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2056</v>
+        <v>0.4931</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.131</v>
+        <v>0.8639</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5729</v>
+        <v>0.1723</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.6916</v>
       </c>
       <c r="G18" t="n">
         <v>0.4184</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7125</v>
+        <v>0.4455</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5486</v>
+        <v>0.1481</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1639</v>
+        <v>0.2974</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9504</v>
+        <v>0.2658</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4786</v>
+        <v>-3.2784</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5283</v>
+        <v>3.5442</v>
       </c>
       <c r="G19" t="n">
         <v>0.1826</v>
@@ -1936,13 +1936,13 @@
         <v>1.7371</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.905</v>
+        <v>-0.6888</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6993</v>
+        <v>-0.499</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2057</v>
+        <v>-0.1897</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0964</v>
+        <v>-0.4215</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5326</v>
+        <v>-2.2321</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4362</v>
+        <v>1.8106</v>
       </c>
       <c r="G20" t="n">
         <v>1.734</v>
@@ -2014,13 +2014,13 @@
         <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1006</v>
+        <v>-0.4257</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7139</v>
+        <v>-0.4134</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3867</v>
+        <v>-0.0123</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5717</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7058</v>
+        <v>-0.8307</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3214</v>
+        <v>-2.2213</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6156</v>
+        <v>1.3906</v>
       </c>
       <c r="G21" t="n">
         <v>2.9491</v>
@@ -2092,13 +2092,13 @@
         <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2037</v>
+        <v>-0.3285</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5803</v>
+        <v>-0.4802</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6233</v>
+        <v>0.1517</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9421</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1079</v>
+        <v>-2.2279</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3201</v>
+        <v>-1.5203</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.7075</v>
       </c>
       <c r="G22" t="n">
         <v>-1.24</v>
@@ -2170,13 +2170,13 @@
         <v>0.193</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0958</v>
+        <v>-0.2158</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2512</v>
+        <v>0.0509</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.347</v>
+        <v>-0.2667</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1848</v>
+        <v>-4.2898</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0848</v>
+        <v>-4.484</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1</v>
+        <v>0.1942</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3488</v>
@@ -2248,13 +2248,13 @@
         <v>0.772</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.199</v>
+        <v>-0.3041</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8923</v>
+        <v>-0.2915</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3067</v>
+        <v>-0.0126</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.3977</v>
+        <v>19.7357</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0808</v>
+        <v>-3.080900000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>19.4787</v>
+        <v>22.8166</v>
       </c>
       <c r="G24" t="n">
         <v>23.0953</v>
@@ -2305,7 +2305,7 @@
         <v>3.073</v>
       </c>
       <c r="L24" t="n">
-        <v>6.9976</v>
+        <v>6.997600000000001</v>
       </c>
       <c r="M24" t="n">
         <v>13.0246</v>
@@ -2314,7 +2314,7 @@
         <v>6.5738</v>
       </c>
       <c r="O24" t="n">
-        <v>6.451</v>
+        <v>6.451000000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-8.685400000000001</v>
@@ -2326,13 +2326,13 @@
         <v>10.6154</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.6223</v>
+        <v>-0.2844000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.690000000000001</v>
+        <v>-2.6899</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9324000000000001</v>
+        <v>2.4057</v>
       </c>
       <c r="V24" t="n">
         <v>5.6105</v>
